--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
   <si>
     <t>界面</t>
   </si>
@@ -413,6 +413,12 @@
     <t>1234567890G:童锁启停电源</t>
   </si>
   <si>
+    <t>1234567890G:</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢</t>
+  </si>
+  <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃洗涤漂洗脱水暂停中打冷风烘干门锁开关</t>
   </si>
   <si>
@@ -420,9 +426,6 @@
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1598,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="9.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" customWidth="1"/>
@@ -2282,7 +2285,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
         <v>128</v>
@@ -2290,7 +2293,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
         <v>129</v>
@@ -2298,7 +2301,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
         <v>130</v>
@@ -2306,10 +2309,18 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>125</v>
+      </c>
+      <c r="B60" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="134">
   <si>
     <t>界面</t>
   </si>
@@ -419,10 +419,13 @@
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃洗涤漂洗脱水暂停中打冷风烘干门锁开关</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
+  </si>
+  <si>
+    <t>请输入特殊出厂序列号</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>
@@ -1598,7 +1601,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="9.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" customWidth="1"/>
@@ -2309,7 +2312,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
         <v>131</v>
@@ -2317,10 +2320,18 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="B60" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -425,7 +425,7 @@
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -425,7 +425,7 @@
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A_ZZT_Project\Xiaoya_Xiyiji\LVGL_zzt_v1.5\lv_port_pc_vscode-master\src\ui\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
@@ -425,7 +430,7 @@
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="135">
   <si>
     <t>界面</t>
   </si>
@@ -418,7 +418,7 @@
     <t>1234567890G:童锁启停电源</t>
   </si>
   <si>
-    <t>1234567890G:</t>
+    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢</t>
@@ -430,7 +430,10 @@
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏</t>
+  </si>
+  <si>
+    <t>1234567890:：</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>
@@ -1606,7 +1609,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultColWidth="9.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" customWidth="1"/>
@@ -2333,10 +2336,18 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>125</v>
+      </c>
+      <c r="B62" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -415,13 +415,13 @@
     <t>按比例放大</t>
   </si>
   <si>
-    <t>1234567890G:童锁启停电源</t>
+    <t>1234567890G:童锁启停电源少量中等多自动</t>
   </si>
   <si>
     <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -421,16 +421,16 @@
     <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
   </si>
   <si>
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改</t>
   </si>
   <si>
     <t>1234567890:：</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -430,7 +430,7 @@
     <t>请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改分钟消</t>
   </si>
   <si>
     <t>1234567890:：</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -415,13 +415,13 @@
     <t>按比例放大</t>
   </si>
   <si>
-    <t>1234567890G:童锁启停电源少量中等多自动</t>
-  </si>
-  <si>
-    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案</t>
+    <t>1234567890G:童锁启停电源少量中等多自动进行已完成</t>
+  </si>
+  <si>
+    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -418,7 +418,7 @@
     <t>1234567890G:童锁启停电源少量中等多自动进行已完成</t>
   </si>
   <si>
-    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成</t>
+    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -415,13 +415,13 @@
     <t>按比例放大</t>
   </si>
   <si>
-    <t>1234567890G:童锁启停电源少量中等多自动进行已完成</t>
+    <t>1234567890G:童锁启停电源少量中等多自动进行已完成开发票订单详情</t>
   </si>
   <si>
     <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情合计</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -415,19 +415,19 @@
     <t>按比例放大</t>
   </si>
   <si>
-    <t>1234567890G:童锁启停电源少量中等多自动进行已完成开发票订单详情</t>
-  </si>
-  <si>
-    <t>1234567890G:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:童锁启停电源少量中等多自动进行已完成开发票订单详情大物脱水标准洗筒洁快分次度转秒</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情合计</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
-  </si>
-  <si>
-    <t>请输入特殊出厂序列号</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•:：洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:：请输入特殊出厂序列号</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改分钟消</t>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -415,10 +415,10 @@
     <t>按比例放大</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:童锁启停电源少量中等多自动进行已完成开发票订单详情大物脱水标准洗筒洁快分次度转秒</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:，可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz: 童锁启停电源少量中等多自动进行已完成开发票订单详情大物脱水标准洗筒洁快分次度转秒</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz;. :，,可设置屏幕进入休眠状态的时间默认分钟一直处于常亮已完成运行过程中如若关闭此功能则在无操作自动熄灭</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-—/ ，,.•：℃￥¥？?（）！!₃、():。*请扫描屏幕上下二维码支付完成功机器自动运行大物单脱水标准洗筒自洁快检测到柔顺涤剂不足及时添加输入管理员密码错误稍后再试设置程序亮度声音控制语言待间恢复默认联系我们确定认取消当前时长漂次数转速温位智能金额重小分钟熄是否需要所有都将出厂正在所有已服务热线鸭专属为您提供优质的体验统切换中英文投臭氧新风护升级网络据修改放开启关闭可调节衣与用量产生来实现高效杀菌毒和去除异味效果卫平内歇性效促进湿气散发保持干爽最版本原两一致过处于常状态如若则无操作灭触控播报方式超秒订查询宝微信查询近条使右打连接最附配传项策略基础感故障日志户记录备仅禁止低中高冷烘却初始追防缠绕避免结均匀选择直点击即总停门锁仍解拨售后工程师业紧未决好或主板松安全口通畅电显示讯坏皮带轮并驱脑源模块断商学习特殊列号型循环头龙摆拉排清软泵滤戒警继续阀频率档溢液界面图案万虹广场店济南楼宿舍豪酒桔子房共件束详情合计</t>
@@ -427,16 +427,16 @@
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz-— .￥¥℃•:：洗涤漂洗脱水暂停中打冷风烘干门锁开关请输入特殊出厂序列号</t>
   </si>
   <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz:：请输入特殊出厂序列号</t>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz :：请输入特殊出厂序列号</t>
   </si>
   <si>
     <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz- .，,！!：:•大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣低中高冷温风检密码错误稍后再试机器设置功配网失败重新连接将在熄屏原输入两次不一致修改分钟消</t>
   </si>
   <si>
-    <t>1234567890:：</t>
-  </si>
-  <si>
-    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ:</t>
+    <t>1234567890 :：</t>
+  </si>
+  <si>
+    <t>1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZ :</t>
   </si>
 </sst>
 </file>

--- a/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
+++ b/lv_port_pc_vscode-master/src/ui/ui_text_strings.xlsx
@@ -32,385 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="135">
-  <si>
-    <t>界面</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>控件/位置</t>
-  </si>
-  <si>
-    <t>建议ID</t>
-  </si>
-  <si>
-    <t>文字内容</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>格式/变量</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>共用顶部栏</t>
-  </si>
-  <si>
-    <t>顶部</t>
-  </si>
-  <si>
-    <t>启停按钮</t>
-  </si>
-  <si>
-    <t>UI_BTN_RUNPAUSE</t>
-  </si>
-  <si>
-    <t>启停</t>
-  </si>
-  <si>
-    <t>固定</t>
-  </si>
-  <si>
-    <t>全界面 x=100</t>
-  </si>
-  <si>
-    <t>电源按钮</t>
-  </si>
-  <si>
-    <t>UI_BTN_POWER</t>
-  </si>
-  <si>
-    <t>电源</t>
-  </si>
-  <si>
-    <t>全界面 x=180</t>
-  </si>
-  <si>
-    <t>状态栏</t>
-  </si>
-  <si>
-    <t>网络</t>
-  </si>
-  <si>
-    <t>UI_STATUS_4G</t>
-  </si>
-  <si>
-    <t>4G</t>
-  </si>
-  <si>
-    <t>WiFi</t>
-  </si>
-  <si>
-    <t>UI_STATUS_WIFI</t>
-  </si>
-  <si>
-    <t>(WiFi图标)</t>
-  </si>
-  <si>
-    <t>符号</t>
-  </si>
-  <si>
-    <t>LV_SYMBOL_WIFI</t>
-  </si>
-  <si>
-    <t>非文字</t>
-  </si>
-  <si>
-    <t>时钟</t>
-  </si>
-  <si>
-    <t>UI_STATUS_CLOCK</t>
-  </si>
-  <si>
-    <t>动态</t>
-  </si>
-  <si>
-    <t>HH:MM</t>
-  </si>
-  <si>
-    <t>每秒更新；初始值16:30</t>
-  </si>
-  <si>
-    <t>主页</t>
-  </si>
-  <si>
-    <t>轮播</t>
-  </si>
-  <si>
-    <t>程序名-大物</t>
-  </si>
-  <si>
-    <t>UI_PROG_DAWU</t>
-  </si>
-  <si>
-    <t>大物</t>
-  </si>
-  <si>
-    <t>卡片为图片无文字</t>
-  </si>
-  <si>
-    <t>程序名-单脱水</t>
-  </si>
-  <si>
-    <t>UI_PROG_DANTUO</t>
-  </si>
-  <si>
-    <t>单脱水</t>
-  </si>
-  <si>
-    <t>程序名-标准洗</t>
-  </si>
-  <si>
-    <t>UI_PROG_BIAOZHUN</t>
-  </si>
-  <si>
-    <t>标准洗</t>
-  </si>
-  <si>
-    <t>默认选中</t>
-  </si>
-  <si>
-    <t>程序名-筒自洁</t>
-  </si>
-  <si>
-    <t>UI_PROG_TONGZIJIE</t>
-  </si>
-  <si>
-    <t>筒自洁</t>
-  </si>
-  <si>
-    <t>程序名-快洗</t>
-  </si>
-  <si>
-    <t>UI_PROG_KUAIXI</t>
-  </si>
-  <si>
-    <t>快洗</t>
-  </si>
-  <si>
-    <t>中部</t>
-  </si>
-  <si>
-    <t>副标题</t>
-  </si>
-  <si>
-    <t>UI_HOME_SUBTITLE</t>
-  </si>
-  <si>
-    <t>自动感知 一键智洗</t>
-  </si>
-  <si>
-    <t>代码中始终隐藏</t>
-  </si>
-  <si>
-    <t>底部</t>
-  </si>
-  <si>
-    <t>洗涤时间</t>
-  </si>
-  <si>
-    <t>UI_HOME_TIME</t>
-  </si>
-  <si>
-    <t>35s</t>
-  </si>
-  <si>
-    <t>{n}s</t>
-  </si>
-  <si>
-    <t>随选中程序变化</t>
-  </si>
-  <si>
-    <t>洗涤温度</t>
-  </si>
-  <si>
-    <t>UI_HOME_TEMP</t>
-  </si>
-  <si>
-    <t>30℃</t>
-  </si>
-  <si>
-    <t>见程序表</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>程序金额</t>
-  </si>
-  <si>
-    <t>UI_HOME_PRICE</t>
-  </si>
-  <si>
-    <t>￥{n}或--</t>
-  </si>
-  <si>
-    <t>筒自洁为--</t>
-  </si>
-  <si>
-    <t>语言</t>
-  </si>
-  <si>
-    <t>UI_HOME_LANG</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>管理员</t>
-  </si>
-  <si>
-    <t>UI_HOME_LOGIN</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>支付页</t>
-  </si>
-  <si>
-    <t>金额</t>
-  </si>
-  <si>
-    <t>UI_PAY_PRICE</t>
-  </si>
-  <si>
-    <t>￥ {n}.00或--</t>
-  </si>
-  <si>
-    <t>随选中程序</t>
-  </si>
-  <si>
-    <t>提示</t>
-  </si>
-  <si>
-    <t>UI_PAY_HINT</t>
-  </si>
-  <si>
-    <t>请扫描屏幕上二维码支付完成机器自动运行</t>
-  </si>
-  <si>
-    <t>建议可换行</t>
-  </si>
-  <si>
-    <t>支付完成页</t>
-  </si>
-  <si>
-    <t>主文案</t>
-  </si>
-  <si>
-    <t>UI_PAY_DONE_TITLE</t>
-  </si>
-  <si>
-    <t>支付完成</t>
-  </si>
-  <si>
-    <t>5秒后自动进运行页</t>
-  </si>
-  <si>
-    <t>运行页</t>
-  </si>
-  <si>
-    <t>程序名</t>
-  </si>
-  <si>
-    <t>UI_RUN_MODE</t>
-  </si>
-  <si>
-    <t>程序名表</t>
-  </si>
-  <si>
-    <t>与主页选中一致</t>
-  </si>
-  <si>
-    <t>倒计时</t>
-  </si>
-  <si>
-    <t>UI_RUN_TIME</t>
-  </si>
-  <si>
-    <t>M:SS</t>
-  </si>
-  <si>
-    <t>暂停时500ms闪烁</t>
-  </si>
-  <si>
-    <t>右侧</t>
-  </si>
-  <si>
-    <t>童锁</t>
-  </si>
-  <si>
-    <t>UI_RUN_CHILD_LOCK</t>
-  </si>
-  <si>
-    <t>长按3s切换</t>
-  </si>
-  <si>
-    <t>底部左</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>UI_RUN_STATUS</t>
-  </si>
-  <si>
-    <t>洗涤中...</t>
-  </si>
-  <si>
-    <t>底部右</t>
-  </si>
-  <si>
-    <t>阶段</t>
-  </si>
-  <si>
-    <t>UI_RUN_STAGES</t>
-  </si>
-  <si>
-    <t>洗涤        漂洗        脱水</t>
-  </si>
-  <si>
-    <t>含空格对齐</t>
-  </si>
-  <si>
-    <t>结束页</t>
-  </si>
-  <si>
-    <t>UI_END_TITLE</t>
-  </si>
-  <si>
-    <t>洗涤完成</t>
-  </si>
-  <si>
-    <t>副提示</t>
-  </si>
-  <si>
-    <t>UI_END_HINT</t>
-  </si>
-  <si>
-    <t>请及时取衣</t>
-  </si>
-  <si>
-    <t>字号</t>
-  </si>
-  <si>
-    <t>1234567890G童锁启停电源</t>
-  </si>
-  <si>
-    <t>￥℃1234567890ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyz洗涤漂洗脱水暂停中请扫描屏幕上二维码支付完成机器自动运行</t>
-  </si>
-  <si>
-    <t>大物单脱水标准洗筒自洁快支付洗涤完成请及时取衣</t>
-  </si>
-  <si>
-    <t>:1234567890</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>按比例放大</t>
   </si>
@@ -1064,16 +686,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1609,746 +1231,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="9.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr defaultColWidth="9.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.4363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
+    <row r="20" spans="5:5">
+      <c r="E20" s="2"/>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
+    <row r="26" spans="5:5">
+      <c r="E26" s="3"/>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.6875</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="2">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="3">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" t="s">
-        <v>45</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G35" t="s">
-        <v>96</v>
-      </c>
-      <c r="H35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" s="1">
-        <v>0.0243055555555556</v>
-      </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>93</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>116</v>
-      </c>
-      <c r="E44" t="s">
-        <v>117</v>
-      </c>
-      <c r="F44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" t="s">
-        <v>118</v>
-      </c>
-      <c r="D45" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48">
-        <v>8</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>14</v>
-      </c>
-      <c r="B49" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>20</v>
-      </c>
-      <c r="B50" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>12</v>
-      </c>
-      <c r="B52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>20</v>
-      </c>
-      <c r="B55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>27</v>
-      </c>
-      <c r="B56" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>30</v>
-      </c>
-      <c r="B57" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>35</v>
-      </c>
-      <c r="B58" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>40</v>
-      </c>
-      <c r="B59" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>50</v>
-      </c>
-      <c r="B60" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>70</v>
-      </c>
-      <c r="B61" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>125</v>
-      </c>
-      <c r="B62" t="s">
-        <v>134</v>
-      </c>
+    <row r="36" spans="5:5">
+      <c r="E36" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
